--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:49</t>
+    <t xml:space="preserve">2026-09-09 22:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:37</t>
+    <t xml:space="preserve">2026-09-18 09:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:59</t>
+    <t xml:space="preserve">2026-09-23 12:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:05</t>
+    <t xml:space="preserve">2026-10-02 13:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:03</t>
+    <t xml:space="preserve">2026-10-05 08:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
